--- a/Schema.xlsx
+++ b/Schema.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Varaanga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC1869A-A645-4360-8282-502659747D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1516161D-CDF9-4D8D-B3E6-5440F4706D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{87B7AB2D-BA21-4C92-92CB-4F5FD6F39074}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="SearchScreen" sheetId="2" r:id="rId2"/>
+    <sheet name="DetailsScreen" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="44">
-  <si>
-    <t>FORM TYPES</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="69">
   <si>
     <t>formtype_id</t>
   </si>
@@ -51,15 +50,6 @@
     <t>formtype_description</t>
   </si>
   <si>
-    <t>Table 1</t>
-  </si>
-  <si>
-    <t>FORMFIELD LABLES</t>
-  </si>
-  <si>
-    <t>Table 2</t>
-  </si>
-  <si>
     <t>Fkey</t>
   </si>
   <si>
@@ -75,12 +65,6 @@
     <t>formfield_order</t>
   </si>
   <si>
-    <t>Table 3</t>
-  </si>
-  <si>
-    <t>CUSTOMER</t>
-  </si>
-  <si>
     <t>customer_id</t>
   </si>
   <si>
@@ -90,21 +74,12 @@
     <t>customer_address</t>
   </si>
   <si>
-    <t>FILLED REPORT</t>
-  </si>
-  <si>
-    <t>Table 4</t>
-  </si>
-  <si>
     <t>report_id</t>
   </si>
   <si>
     <t>formfield_value</t>
   </si>
   <si>
-    <t>Table 5</t>
-  </si>
-  <si>
     <t>report_date</t>
   </si>
   <si>
@@ -114,12 +89,6 @@
     <t>report_done_by</t>
   </si>
   <si>
-    <t>REPORT METADATA</t>
-  </si>
-  <si>
-    <t>Table 6</t>
-  </si>
-  <si>
     <t>varchar20</t>
   </si>
   <si>
@@ -132,9 +101,6 @@
     <t>version_id</t>
   </si>
   <si>
-    <t>REPORT AUTHOR</t>
-  </si>
-  <si>
     <t>author_id</t>
   </si>
   <si>
@@ -144,12 +110,6 @@
     <t>license_no</t>
   </si>
   <si>
-    <t>REPORT GENERATION</t>
-  </si>
-  <si>
-    <t>Table 7</t>
-  </si>
-  <si>
     <t>generation_id</t>
   </si>
   <si>
@@ -157,14 +117,139 @@
   </si>
   <si>
     <t>generated_by</t>
+  </si>
+  <si>
+    <t>FORM TYPES (Table 1)</t>
+  </si>
+  <si>
+    <t>FORMFIELD LABLES ( Table 2)</t>
+  </si>
+  <si>
+    <t>CUSTOMER (Table 3)</t>
+  </si>
+  <si>
+    <t>FILLED REPORT (Table 4)</t>
+  </si>
+  <si>
+    <t>REPORT METADATA (Table 5)</t>
+  </si>
+  <si>
+    <t>REPORT AUTHOR (Table 6)</t>
+  </si>
+  <si>
+    <t>REPORT GENERATION (Table 7)</t>
+  </si>
+  <si>
+    <t>not null</t>
+  </si>
+  <si>
+    <t>Criteria</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Report Date</t>
+  </si>
+  <si>
+    <t>Form Type</t>
+  </si>
+  <si>
+    <t>Report Status</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>&lt;text box supported with a find button, on click of find button a pop up will come up showing the companies&gt;</t>
+  </si>
+  <si>
+    <t>&lt; Type of Form&gt;</t>
+  </si>
+  <si>
+    <t>Field label 1</t>
+  </si>
+  <si>
+    <t>&lt;text box&gt;</t>
+  </si>
+  <si>
+    <t>Field label 2</t>
+  </si>
+  <si>
+    <t>&lt;Search button&gt; - on click of this button populate the grid below, based on the company selected by the user in the text box above.</t>
+  </si>
+  <si>
+    <t>&lt;page number&gt;</t>
+  </si>
+  <si>
+    <t>- first try for laptop screen then make it responsive screen</t>
+  </si>
+  <si>
+    <t>&lt;Add Button&gt; - on click of this button open the Details screen with blank fields</t>
+  </si>
+  <si>
+    <t>&lt;Details button&gt; - on click of this button, display the Details screen for the selected row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;print button&gt; - to print the selected row </t>
+  </si>
+  <si>
+    <t>- the above grid will be like a tree structure. Meaning grouped by company, report date</t>
+  </si>
+  <si>
+    <t>eg</t>
+  </si>
+  <si>
+    <t>+ xyz company</t>
+  </si>
+  <si>
+    <t>+ 12th Dec 2024</t>
+  </si>
+  <si>
+    <t>Report ID</t>
+  </si>
+  <si>
+    <t>Reportid</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>final</t>
+  </si>
+  <si>
+    <t>bcd</t>
+  </si>
+  <si>
+    <t>+ 20th Dec 2025</t>
+  </si>
+  <si>
+    <t>ced</t>
+  </si>
+  <si>
+    <t>hhh</t>
+  </si>
+  <si>
+    <t>+ alphabet company</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -192,8 +277,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,255 +598,489 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91C3623C-0410-4A63-BD69-5BC921C8EF9F}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="5" max="5" width="18.109375" customWidth="1"/>
     <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1"/>
+      <c r="M1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
         <v>8</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
         <v>9</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="I9:J9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{047C5DEE-AA37-46DD-B377-46C7B7BAD960}">
+  <dimension ref="D5:S29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="5" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="4:18" x14ac:dyDescent="0.3">
+      <c r="J11" t="s">
+        <v>53</v>
+      </c>
+      <c r="R11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="G18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21" t="s">
+        <v>56</v>
+      </c>
+      <c r="N21" t="s">
+        <v>39</v>
+      </c>
+      <c r="O21" t="s">
+        <v>40</v>
+      </c>
+      <c r="P21" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>41</v>
+      </c>
+      <c r="R21" t="s">
+        <v>42</v>
+      </c>
+      <c r="S21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="D22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="O23" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>8</v>
+      </c>
+      <c r="R24" t="s">
+        <v>61</v>
+      </c>
+      <c r="S24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="P25">
+        <v>2</v>
+      </c>
+      <c r="Q25">
+        <v>8</v>
+      </c>
+      <c r="R25" t="s">
+        <v>63</v>
+      </c>
+      <c r="S25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="O26" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="P27">
         <v>10</v>
       </c>
-      <c r="I1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="Q27">
+        <v>8</v>
+      </c>
+      <c r="R27" t="s">
+        <v>63</v>
+      </c>
+      <c r="S27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="P28">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" t="s">
-        <v>6</v>
-      </c>
-      <c r="M5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
+      <c r="Q28">
+        <v>8</v>
+      </c>
+      <c r="R28" t="s">
+        <v>63</v>
+      </c>
+      <c r="S28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="4:19" x14ac:dyDescent="0.3">
+      <c r="N29" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEF21E4-8937-4258-ADCE-D4E78FE1CD40}">
+  <dimension ref="E6:F8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="17.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E6" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" t="s">
-        <v>2</v>
-      </c>
-      <c r="I11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" t="s">
-        <v>5</v>
-      </c>
-      <c r="I12" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" t="s">
-        <v>5</v>
-      </c>
-      <c r="I13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
